--- a/AAII_Financials/Quarterly/MVST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MVST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>MVST</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="2">
+      <c r="AC7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E8" s="3">
         <v>60600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>96400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>123300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>116500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>113400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>101400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>83700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>104600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>80100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>47000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>64400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>66800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>48100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6900</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E9" s="3">
         <v>41500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>76900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>59600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>73500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>67800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>64100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>62200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>63500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>62600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>36700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>65600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>72800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5700</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E10" s="3">
         <v>19200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>33500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>43000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4800</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-35900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-6700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1200</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E12" s="3">
         <v>8800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1232,82 +1252,85 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>34100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>86800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-3500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-200</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1315,43 +1338,43 @@
         <v>8100</v>
       </c>
       <c r="E15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F15" s="3">
         <v>8400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>8300</v>
       </c>
       <c r="G15" s="3">
         <v>8300</v>
       </c>
       <c r="H15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I15" s="3">
         <v>8000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>7700</v>
       </c>
       <c r="M15" s="3">
         <v>7700</v>
       </c>
       <c r="N15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="O15" s="3">
         <v>5000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>5100</v>
       </c>
       <c r="P15" s="3">
         <v>5100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E17" s="3">
         <v>68500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>94000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>108400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>81900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>102600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>108700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>97100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>95600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>105000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>127600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>106500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>102400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>78300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>75700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>109400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>114400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>150200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>55700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>51800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16800</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-27500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-34600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-45000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-43200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-47600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-113300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-22300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,163 +1647,167 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-57000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-42800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14600</v>
       </c>
-      <c r="G20" s="3">
-        <v>114200</v>
-      </c>
       <c r="H20" s="3">
+        <v>113800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-47500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>82000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>57100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>53600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-96500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="I21" s="3">
         <v>69400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-69500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-22600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-30800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-38100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-40400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-110100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1780,43 +1817,46 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E22" s="3">
         <v>1200</v>
       </c>
       <c r="F22" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G22" s="3">
         <v>1300</v>
       </c>
       <c r="H22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>500</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
@@ -1825,147 +1865,153 @@
         <v>500</v>
       </c>
       <c r="Q22" s="3">
+        <v>500</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
-      </c>
-      <c r="T22" s="3">
-        <v>800</v>
       </c>
       <c r="U22" s="3">
         <v>800</v>
       </c>
       <c r="V22" s="3">
+        <v>800</v>
+      </c>
+      <c r="W22" s="3">
         <v>1200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1500</v>
       </c>
       <c r="X22" s="3">
         <v>1500</v>
       </c>
       <c r="Y22" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="Z22" s="3">
         <v>1400</v>
       </c>
       <c r="AA22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>1500</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>48200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-105800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>61800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-82300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-101600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-43800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-47000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-116400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
         <v>-6300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1978,11 +2024,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
@@ -1990,8 +2036,8 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2003,34 +2049,37 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>48200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-106100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>61800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-82300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-101600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-36500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-43800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-46600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-116500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-27100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD26" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>48200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-106100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>61800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-82300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-101600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24600</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-26100</v>
       </c>
       <c r="O27" s="3">
         <v>-26100</v>
       </c>
       <c r="P27" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-33700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-43800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-46600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-120000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-39100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E32" s="3">
         <v>57000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>42800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-114200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-113800</v>
+      </c>
+      <c r="I32" s="3">
         <v>47500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-82000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>48200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-106100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>61800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-82300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-101600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-26100</v>
       </c>
       <c r="O33" s="3">
         <v>-26100</v>
       </c>
       <c r="P33" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-33700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-43800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-46600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-120000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-39100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>48200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-106100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>61800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-82300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-101600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-26100</v>
       </c>
       <c r="O35" s="3">
         <v>-26100</v>
       </c>
       <c r="P35" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-33700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-43800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-46600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-120000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-39100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC38" s="2">
+      <c r="AC38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,74 +3178,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E41" s="3">
         <v>126100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>105000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>90700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>39500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>67400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>142800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>231400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>295800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>333900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>416200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>480900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>572600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3172,11 +3259,14 @@
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3184,11 +3274,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3196,11 +3286,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3208,23 +3298,23 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>6600</v>
-      </c>
-      <c r="N42" s="3">
-        <v>25500</v>
       </c>
       <c r="O42" s="3">
         <v>25500</v>
       </c>
       <c r="P42" s="3">
+        <v>25500</v>
+      </c>
+      <c r="Q42" s="3">
         <v>25300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3237,8 +3327,8 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E43" s="3">
         <v>129100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>170000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>150800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>130100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>146000</v>
       </c>
       <c r="I43" s="3">
         <v>146000</v>
       </c>
       <c r="J43" s="3">
+        <v>146000</v>
+      </c>
+      <c r="K43" s="3">
         <v>132500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>115800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>177500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>136500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>123800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>110100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>124200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>87200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>135400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>104700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>104300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>85500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3341,74 +3434,77 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E44" s="3">
         <v>95000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>89400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>126900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>141700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>129100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>143300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>157800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>152500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>137300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>149700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>126900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>86800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>87700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>84300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>82300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>64500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>58100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>53400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>47800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>55400</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3424,74 +3520,77 @@
       <c r="AC44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>11500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>80100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>102200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>77600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>74300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>68000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>26100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3504,77 +3603,80 @@
       <c r="AB45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>374900</v>
+      </c>
+      <c r="E46" s="3">
         <v>425800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>448700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>445300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>434600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>448000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>428000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>437600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>418000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>378200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>425600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>403900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>427000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>497000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>545100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>567500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>611400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>653200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>706600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>750900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>180400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3587,11 +3689,14 @@
       <c r="AB46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD46" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3634,8 +3739,8 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3671,76 +3776,79 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>280100</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>543400</v>
+      </c>
+      <c r="E48" s="3">
         <v>526800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>525400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>542100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>540900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>503400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>495800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>523500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>539000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>635300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>640200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>569200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>518800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>461500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>351500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>301900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>295600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>289600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>253100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>222800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>217700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3765,65 +3876,65 @@
         <v>13700</v>
       </c>
       <c r="E49" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F49" s="3">
         <v>13800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1800</v>
       </c>
       <c r="T49" s="3">
         <v>1800</v>
       </c>
       <c r="U49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V49" s="3">
         <v>1900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2100</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,74 +4122,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E52" s="3">
         <v>15700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>86700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>101800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>63000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>54100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4085,11 +4205,14 @@
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,74 +4294,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>952200</v>
+      </c>
+      <c r="E54" s="3">
         <v>987500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1005400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1013600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1004700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>982900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>951900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>997900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>984600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1040600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1096700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1016600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>997700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1004000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>985000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>972900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>971600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>998700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>995300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>990400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>414800</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4251,11 +4377,14 @@
       <c r="AB54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD54" s="3">
         <v>280500</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,74 +4446,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E57" s="3">
         <v>46400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>47000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>72500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>64900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>65600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>83100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>112600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>95300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>32000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>43800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
@@ -4396,77 +4527,80 @@
       <c r="AB57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E58" s="3">
         <v>284400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>315100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>337900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>311700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>137600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>125500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>125700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>106900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>101200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>66600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>71200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>92200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>85800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>109100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>114700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>84000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>74300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>66000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>78700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4479,77 +4613,80 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E59" s="3">
         <v>90000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>108100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>123400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>123000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>114100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>124200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>168300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>164800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>168100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>160000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>153600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>130900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>86800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>65400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>60900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>51100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>38900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4562,77 +4699,80 @@
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E60" s="3">
         <v>444100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>488300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>530000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>524700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>339900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>330200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>335900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>372500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>366600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>403400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>336400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>292700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>277800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>252400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>231800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>226300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>181400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>175600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>153600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>161400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4645,64 +4785,67 @@
       <c r="AB60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E61" s="3">
         <v>41600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>91200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>91500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>158800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>203400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>137300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>107000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>102400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>104000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>91700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>92900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>88800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>72900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>81800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43900</v>
-      </c>
-      <c r="T61" s="3">
-        <v>73100</v>
       </c>
       <c r="U61" s="3">
         <v>73100</v>
@@ -4711,11 +4854,11 @@
         <v>73100</v>
       </c>
       <c r="W61" s="3">
+        <v>73100</v>
+      </c>
+      <c r="X61" s="3">
         <v>169200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4731,74 +4874,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E62" s="3">
         <v>29700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>46700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>86800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>59900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>46800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>114400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4811,11 +4957,14 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,74 +5218,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>409100</v>
+      </c>
+      <c r="E66" s="3">
         <v>521400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>594900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>655500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>648600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>528700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>564000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>511800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>506500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>494500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>532500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>449200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>418000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>398200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>372000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>357100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>317600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>341300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>308600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>273600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>540900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5143,11 +5301,14 @@
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD66" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5406,11 +5574,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>325200</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,74 +5680,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1079900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1067900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1116100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1132700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1131200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1025100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1086900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1004600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-994700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-916300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-891500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-866900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-840800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-814700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-785100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-751400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-714900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-670700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-626100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-579400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-459400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5589,11 +5763,14 @@
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,74 +6024,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>543100</v>
+      </c>
+      <c r="E76" s="3">
         <v>466100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>410500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>358100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>356100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>454200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>387900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>486100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>478100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>546100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>564200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>565300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>577700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>603700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>613000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>615900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>654000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>657400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>686700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>716800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-451300</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5921,11 +6107,14 @@
       <c r="AB76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD76" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC80" s="2">
+      <c r="AC80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>48200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-106100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>61800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-82300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-101600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-26100</v>
       </c>
       <c r="O81" s="3">
         <v>-26100</v>
       </c>
       <c r="P81" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-33700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-43800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-46600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-120000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-39100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6407,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7500</v>
       </c>
       <c r="I83" s="3">
         <v>7500</v>
       </c>
       <c r="J83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K83" s="3">
         <v>4800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4900</v>
       </c>
       <c r="L83" s="3">
         <v>4900</v>
       </c>
       <c r="M83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N83" s="3">
         <v>4700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>37200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>9800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5500</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-57700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-66200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-47100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-91200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-41100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10900</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7228,8 +7462,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7759,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E100" s="3">
         <v>29300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>22200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>20900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>38100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-9400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>597900</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4500</v>
-      </c>
-      <c r="T101" s="3">
-        <v>600</v>
       </c>
       <c r="U101" s="3">
         <v>600</v>
       </c>
       <c r="V101" s="3">
+        <v>600</v>
+      </c>
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E102" s="3">
         <v>4800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-81100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-90200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-113100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-73800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-65400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-76400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>578700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4300</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
     </row>
